--- a/Plantillas/PlantillaDocumentaciónDiagramaPaquetes.xlsx
+++ b/Plantillas/PlantillaDocumentaciónDiagramaPaquetes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28706"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29910"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Luciana\Documents\Estructura\1. Artefactos proyecto\1.2. Artefactos técnicos\1.2.2. Diseño detallado\1.2.2.3. Diagrama de paquetes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:101_{4D839B2C-C55B-456C-A570-9CF0466C3822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F8DC3FE-8794-409F-B5CE-810D275D857F}"/>
+  <xr:revisionPtr revIDLastSave="156" documentId="13_ncr:101_{4D839B2C-C55B-456C-A570-9CF0466C3822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{266D2AC4-159C-446C-BC38-9E25AB088819}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" xr2:uid="{89DBD8A5-DC87-4190-9617-E764C549D606}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{89DBD8A5-DC87-4190-9617-E764C549D606}"/>
   </bookViews>
   <sheets>
     <sheet name="Diagrama Paquetes" sheetId="7" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
   <si>
     <t>En esta hoja se ubica la imagen del modelo, asegurando que sea clara y legible</t>
   </si>
@@ -75,121 +75,127 @@
     <t>src</t>
   </si>
   <si>
-    <t>Paquete raíz que contiene toda la aplicación.</t>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Carpeta raíz que contiene todo el código fuente del servidor.</t>
+  </si>
+  <si>
+    <t>apps/api</t>
+  </si>
+  <si>
+    <t>Punto de entrada de la API. Configura el servidor y los servicios globales.</t>
+  </si>
+  <si>
+    <t>contexts</t>
+  </si>
+  <si>
+    <t>controllers</t>
   </si>
   <si>
     <t>api</t>
   </si>
   <si>
-    <t>Paquete que gestiona las interfaces de comunicación HTTP.</t>
-  </si>
-  <si>
-    <t>controller</t>
-  </si>
-  <si>
-    <t>Paquete que contiene los controladores para manejar las solicitudes HTTP.</t>
+    <t>Reciben las peticiones del usuario y llaman a la lógica necesaria.</t>
+  </si>
+  <si>
+    <t>useCases</t>
+  </si>
+  <si>
+    <t>middlewares</t>
+  </si>
+  <si>
+    <t>Capas de seguridad (ej: validar Token) y control de errores.</t>
+  </si>
+  <si>
+    <t>shared/domain</t>
   </si>
   <si>
     <t>routes</t>
   </si>
   <si>
-    <t>Paquete que define las rutas de la aplicación.</t>
-  </si>
-  <si>
-    <t>application</t>
-  </si>
-  <si>
-    <t>Paquete que contiene la lógica de negocio y los casos de uso.</t>
-  </si>
-  <si>
-    <t>dominio, infraestructure</t>
-  </si>
-  <si>
-    <t>services</t>
-  </si>
-  <si>
-    <t>Paquete que gestiona los servicios de la aplicación.</t>
-  </si>
-  <si>
-    <t>interface</t>
-  </si>
-  <si>
-    <t>Paquete que define las interfaces de los servicios.</t>
-  </si>
-  <si>
-    <t>implementation</t>
-  </si>
-  <si>
-    <t>Paquete que contiene las implementaciones de las interfaces de servicios.</t>
-  </si>
-  <si>
-    <t>use case</t>
-  </si>
-  <si>
-    <t>Paquete que gestiona la lógica de los casos de uso.</t>
-  </si>
-  <si>
-    <t>Paquete que define las interfaces de los casos de uso.</t>
-  </si>
-  <si>
-    <t>Paquete que contiene las implementaciones de los casos de uso.</t>
-  </si>
-  <si>
-    <t>assemblers</t>
-  </si>
-  <si>
-    <t>Paquete que se encarga de transformar datos entre entidades y DTOs.</t>
-  </si>
-  <si>
-    <t>infrastructure</t>
-  </si>
-  <si>
-    <t>Paquete que contiene la configuración e implementación de la infraestructura.</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>Paquete que contiene las implementaciones concretas de almacenamiento de datos.</t>
-  </si>
-  <si>
-    <t>Paquete que define las interfaces para la persistencia de datos.</t>
-  </si>
-  <si>
-    <t>almacenamiento</t>
-  </si>
-  <si>
-    <t>Paquete que contiene la lógica para almacenar datos en sistemas de archivos u otros medios.</t>
-  </si>
-  <si>
-    <t>SQL</t>
-  </si>
-  <si>
-    <t>Paquete que contiene la implementación de la persistencia en bases de datos SQL.</t>
-  </si>
-  <si>
-    <t>dto</t>
-  </si>
-  <si>
-    <t>Paquete que contiene los objetos de transferencia de datos.</t>
-  </si>
-  <si>
-    <t>dominio</t>
-  </si>
-  <si>
-    <t>Paquete que gestiona las reglas de negocio y las entidades del dominio.</t>
-  </si>
-  <si>
-    <t>entities</t>
-  </si>
-  <si>
-    <t>Paquete que contiene las entidades del dominio.</t>
-  </si>
-  <si>
-    <t>business</t>
-  </si>
-  <si>
-    <t>Paquete que contiene la lógica de negocio principal.</t>
+    <t>Define las URLs (endpoints) disponibles en la aplicación.</t>
+  </si>
+  <si>
+    <t>Carpeta principal que agrupa toda la lógica por módulos de negocio.</t>
+  </si>
+  <si>
+    <t>shared</t>
+  </si>
+  <si>
+    <t>Código compartido y herramientas comunes para todo el proyecto.</t>
+  </si>
+  <si>
+    <t>domain (shared)</t>
+  </si>
+  <si>
+    <t>Reglas globales del sistema.</t>
+  </si>
+  <si>
+    <t>infra (shared)</t>
+  </si>
+  <si>
+    <t>Implementaciones técnicas de servicios externos y configuración.</t>
+  </si>
+  <si>
+    <t>config</t>
+  </si>
+  <si>
+    <t>Gestión de la conexión a la base de datos (PostgreSQL/MySQL).</t>
+  </si>
+  <si>
+    <t>env</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>Lógica para enviar correos electrónicos a través de Nodemailer.</t>
+  </si>
+  <si>
+    <t>payment</t>
+  </si>
+  <si>
+    <t>Integración con la pasarela de pagos Wompi.</t>
+  </si>
+  <si>
+    <t>upload</t>
+  </si>
+  <si>
+    <t>Manejo de archivos y almacenamiento de documentos (RUT, etc).</t>
+  </si>
+  <si>
+    <t>user / business / branch / quotation / subscription / notification / collaborator</t>
+  </si>
+  <si>
+    <t>Módulos específicos del negocio. Cada uno representa una funcionalidad core.</t>
+  </si>
+  <si>
+    <t>domain</t>
+  </si>
+  <si>
+    <t>un contexto (ej: user)</t>
+  </si>
+  <si>
+    <t>Entidades (tablas), modelos y reglas propias de ese módulo.</t>
+  </si>
+  <si>
+    <t>Los procesos o servicios específicos (ej: Registrar, Login).</t>
+  </si>
+  <si>
+    <t>infraestructure</t>
+  </si>
+  <si>
+    <t>Repositorios de base de datos (TypeORM) de ese módulo.</t>
+  </si>
+  <si>
+    <t>domain, config</t>
+  </si>
+  <si>
+    <t>interfaces</t>
+  </si>
+  <si>
+    <t>DTOs (objetos de transferencia) y validadores de datos.</t>
   </si>
 </sst>
 </file>
@@ -349,7 +355,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -383,6 +389,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -401,8 +410,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -432,21 +439,24 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Imagen 2">
+        <xdr:cNvPr id="4" name="Imagen 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4FEF69DF-CC7B-3898-D8F4-00EA73C6978E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF1C1B45-F501-D63C-95C1-122509FC0D87}"/>
+            </a:ext>
+            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
+              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{4FEF69DF-CC7B-3898-D8F4-00EA73C6978E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -462,8 +472,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="457200"/>
-          <a:ext cx="11010900" cy="5829300"/>
+          <a:off x="0" y="1257300"/>
+          <a:ext cx="13106400" cy="7286625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -795,7 +805,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9711F7B-CB2F-41BF-88AA-A7043145A5E1}">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
@@ -804,40 +814,40 @@
     <col min="4" max="4" width="22.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="13"/>
-      <c r="D1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="15"/>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:5">
       <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="17"/>
       <c r="E2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="32.25" customHeight="1">
+    <row r="3" spans="1:5" ht="32.25" customHeight="1">
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="19"/>
       <c r="E3" s="1"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:5">
       <c r="A4" s="7" t="s">
         <v>7</v>
       </c>
@@ -851,307 +861,256 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:5">
       <c r="A5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="11"/>
-    </row>
-    <row r="6" spans="1:7">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="2" t="str">
-        <f>A5</f>
-        <v>src</v>
+        <v>14</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="11" t="str">
-        <f>A9</f>
-        <v>application</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="30.75">
+        <v>15</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="2" t="str">
-        <f>A6</f>
-        <v>api</v>
+        <v>17</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="11"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2" t="str">
-        <f>A6</f>
-        <v>api</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="11" t="str">
-        <f>A7</f>
-        <v>controller</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="2" t="str">
-        <f>A5</f>
-        <v>src</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="96" customHeight="1">
+      <c r="A18" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="2" t="str">
-        <f>A9</f>
-        <v>application</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D10" s="11"/>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="2" t="str">
-        <f>A10</f>
-        <v>services</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="11"/>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="2" t="str">
-        <f>A11</f>
-        <v>interface</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="B20" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D22" s="11" t="s">
         <v>27</v>
-      </c>
-      <c r="D12" s="11" t="str">
-        <f>A11</f>
-        <v>interface</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="2" t="str">
-        <f>A9</f>
-        <v>application</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2" t="str">
-        <f>A13</f>
-        <v>use case</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="G14" s="19"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2" t="str">
-        <f>A13</f>
-        <v>use case</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D15" s="11" t="str">
-        <f>A14</f>
-        <v>interface</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2" t="str">
-        <f>A9</f>
-        <v>application</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D16" s="11"/>
-    </row>
-    <row r="17" spans="1:8" ht="30.75">
-      <c r="A17" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2" t="str">
-        <f>A5</f>
-        <v>src</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="11" t="str">
-        <f>B18</f>
-        <v>infrastructure</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="30.75">
-      <c r="A18" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="2" t="str">
-        <f>A17</f>
-        <v>infrastructure</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D18" s="11" t="str">
-        <f>A19</f>
-        <v>interface</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="2" t="str">
-        <f>A18</f>
-        <v>data</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="11"/>
-    </row>
-    <row r="20" spans="1:8" ht="30.75">
-      <c r="A20" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="2" t="str">
-        <f>A18</f>
-        <v>data</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="11" t="str">
-        <f>A19</f>
-        <v>interface</v>
-      </c>
-      <c r="H20" s="20"/>
-    </row>
-    <row r="21" spans="1:8" ht="30.75">
-      <c r="A21" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="2" t="str">
-        <f>A18</f>
-        <v>data</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D21" s="11" t="str">
-        <f>A19</f>
-        <v>interface</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
-      <c r="A22" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2" t="str">
-        <f>A5</f>
-        <v>src</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="D22" s="11"/>
-    </row>
-    <row r="23" spans="1:8">
-      <c r="A23" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" s="2" t="str">
-        <f>A5</f>
-        <v>src</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" s="11"/>
-    </row>
-    <row r="24" spans="1:8">
-      <c r="A24" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="str">
-        <f>A23</f>
-        <v>dominio</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D24" s="11"/>
-    </row>
-    <row r="25" spans="1:8">
-      <c r="A25" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" s="2" t="str">
-        <f>A5</f>
-        <v>src</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" s="11" t="str">
-        <f>A9</f>
-        <v>application</v>
       </c>
     </row>
   </sheetData>
@@ -1166,6 +1125,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="36cf0646-7300-4608-bcc3-e29ed014863a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="734bc881-a844-4d86-9741-49f87248cc41" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -1174,9 +1144,9 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101001945CC36234B18439988D70FCB761011" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="49d1d5a573ca54dccef2d71c1bfe4d0c">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="36cf0646-7300-4608-bcc3-e29ed014863a" xmlns:ns3="734bc881-a844-4d86-9741-49f87248cc41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="fb428a4efaeddf2ef8bccbe6d8f13bc5" ns2:_="" ns3:_="">
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101001945CC36234B18439988D70FCB761011" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="8ca733e0ec3c0df6e34813901e7a3ca5">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="36cf0646-7300-4608-bcc3-e29ed014863a" xmlns:ns3="734bc881-a844-4d86-9741-49f87248cc41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="aed9a3083501fe1d9ea761da13b3b1bf" ns2:_="" ns3:_="">
     <xsd:import namespace="36cf0646-7300-4608-bcc3-e29ed014863a"/>
     <xsd:import namespace="734bc881-a844-4d86-9741-49f87248cc41"/>
     <xsd:element name="properties">
@@ -1369,27 +1339,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="36cf0646-7300-4608-bcc3-e29ed014863a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="734bc881-a844-4d86-9741-49f87248cc41" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9C46951-82F9-470A-B593-5307BF23E49F}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{242E59AD-DB22-4806-BD1F-124BBFC1FD43}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AD007B5C-5670-49E8-B517-5A02A780688B}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9C46951-82F9-470A-B593-5307BF23E49F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EF36810-CC0A-4552-9720-30EAD2DF5919}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
